--- a/Datasets_list.xlsx
+++ b/Datasets_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MFI\Documents\GitHub\ML_Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0022787-E864-408E-ACDE-EB4EDC56364A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCF2B6E2-431D-4320-A574-0ACF72D0E735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{587159C4-2FA1-4D2B-B11E-F39C1D96C62B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Name</t>
   </si>
@@ -105,6 +105,9 @@
   </si>
   <si>
     <t>Rice Classification</t>
+  </si>
+  <si>
+    <t>Glass</t>
   </si>
 </sst>
 </file>
@@ -485,7 +488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5F5E0D8-AFDE-4C18-BDE5-CE4646C92338}">
-  <dimension ref="A3:H18"/>
+  <dimension ref="A3:H19"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="30.265625" customWidth="1"/>
@@ -575,78 +578,75 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A6">
-        <v>3</v>
-      </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H6">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C7">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D7">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="E7">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G7">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="H7">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C8">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D8">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="E8">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="F8">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G8">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="H8">
         <v>50</v>
@@ -654,77 +654,77 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C9">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D9">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="E9">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G9">
         <v>50</v>
       </c>
       <c r="H9">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C10">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D10">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E10">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F10">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G10">
         <v>50</v>
       </c>
       <c r="H10">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C11">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D11">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E11">
         <v>20</v>
       </c>
       <c r="F11">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="G11">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="H11">
         <v>60</v>
@@ -732,39 +732,39 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="C12">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D12">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="E12">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F12">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G12">
         <v>70</v>
       </c>
       <c r="H12">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C13">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D13">
         <v>80</v>
@@ -773,36 +773,36 @@
         <v>50</v>
       </c>
       <c r="F13">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="G13">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H13">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D14">
         <v>80</v>
       </c>
       <c r="E14">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="F14">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="G14">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H14">
         <v>70</v>
@@ -810,105 +810,131 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="F15">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="G15">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="H15">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C16">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="E16">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F16">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="G16">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="H16">
-        <v>85</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A17">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C17">
         <v>70</v>
       </c>
       <c r="D17">
+        <v>70</v>
+      </c>
+      <c r="E17">
+        <v>80</v>
+      </c>
+      <c r="F17">
+        <v>80</v>
+      </c>
+      <c r="G17">
+        <v>80</v>
+      </c>
+      <c r="H17">
         <v>85</v>
-      </c>
-      <c r="E17">
-        <v>50</v>
-      </c>
-      <c r="F17">
-        <v>75</v>
-      </c>
-      <c r="G17">
-        <v>90</v>
-      </c>
-      <c r="H17">
-        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A18">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C18">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="D18">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E18">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F18">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G18">
         <v>90</v>
       </c>
       <c r="H18">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A19">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19">
+        <v>90</v>
+      </c>
+      <c r="D19">
+        <v>80</v>
+      </c>
+      <c r="E19">
+        <v>70</v>
+      </c>
+      <c r="F19">
+        <v>80</v>
+      </c>
+      <c r="G19">
+        <v>90</v>
+      </c>
+      <c r="H19">
         <v>95</v>
       </c>
     </row>

--- a/Datasets_list.xlsx
+++ b/Datasets_list.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MFI\Documents\GitHub\ML_Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCF2B6E2-431D-4320-A574-0ACF72D0E735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C02A1D7-7C77-4A48-8206-2DB01F306A45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{587159C4-2FA1-4D2B-B11E-F39C1D96C62B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Name</t>
   </si>
@@ -108,13 +108,25 @@
   </si>
   <si>
     <t>Glass</t>
+  </si>
+  <si>
+    <t>Logistics</t>
+  </si>
+  <si>
+    <t>XXXX</t>
+  </si>
+  <si>
+    <t>XXXXX</t>
+  </si>
+  <si>
+    <t>xXXXXXX</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -126,6 +138,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -151,9 +170,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -488,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5F5E0D8-AFDE-4C18-BDE5-CE4646C92338}">
-  <dimension ref="A3:H19"/>
+  <dimension ref="A3:H23"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="30.265625" customWidth="1"/>
@@ -578,25 +598,26 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B6" t="s">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
+      <c r="C6" s="2">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
         <v>30</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="2">
         <v>35</v>
       </c>
     </row>
@@ -627,52 +648,39 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A8">
-        <v>4</v>
-      </c>
-      <c r="B8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8">
-        <v>50</v>
-      </c>
-      <c r="D8">
-        <v>70</v>
-      </c>
-      <c r="E8">
-        <v>70</v>
-      </c>
-      <c r="F8">
-        <v>50</v>
-      </c>
-      <c r="G8">
-        <v>55</v>
-      </c>
-      <c r="H8">
-        <v>50</v>
+      <c r="B8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2">
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C9">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D9">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="E9">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="F9">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G9">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="H9">
         <v>50</v>
@@ -680,77 +688,77 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C10">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D10">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="E10">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G10">
         <v>50</v>
       </c>
       <c r="H10">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C11">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D11">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E11">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F11">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G11">
         <v>50</v>
       </c>
       <c r="H11">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C12">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D12">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E12">
         <v>20</v>
       </c>
       <c r="F12">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="G12">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="H12">
         <v>60</v>
@@ -758,184 +766,251 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="C13">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D13">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="E13">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F13">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G13">
         <v>70</v>
       </c>
       <c r="H13">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A14">
-        <v>10</v>
-      </c>
-      <c r="B14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14">
-        <v>25</v>
-      </c>
-      <c r="D14">
-        <v>80</v>
-      </c>
-      <c r="E14">
-        <v>50</v>
-      </c>
-      <c r="F14">
-        <v>50</v>
-      </c>
-      <c r="G14">
-        <v>75</v>
-      </c>
-      <c r="H14">
-        <v>70</v>
+      <c r="A14" s="2"/>
+      <c r="B14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2">
+        <v>62.5</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A15">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D15">
         <v>80</v>
       </c>
       <c r="E15">
+        <v>50</v>
+      </c>
+      <c r="F15">
+        <v>80</v>
+      </c>
+      <c r="G15">
+        <v>70</v>
+      </c>
+      <c r="H15">
         <v>65</v>
-      </c>
-      <c r="F15">
-        <v>80</v>
-      </c>
-      <c r="G15">
-        <v>80</v>
-      </c>
-      <c r="H15">
-        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D16">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F16">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G16">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="H16">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A17">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>80</v>
+      </c>
+      <c r="E17">
+        <v>65</v>
+      </c>
+      <c r="F17">
+        <v>80</v>
+      </c>
+      <c r="G17">
+        <v>80</v>
+      </c>
+      <c r="H17">
         <v>70</v>
-      </c>
-      <c r="D17">
-        <v>70</v>
-      </c>
-      <c r="E17">
-        <v>80</v>
-      </c>
-      <c r="F17">
-        <v>80</v>
-      </c>
-      <c r="G17">
-        <v>80</v>
-      </c>
-      <c r="H17">
-        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A18">
+        <v>12</v>
+      </c>
+      <c r="B18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>10</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>10</v>
+      </c>
+      <c r="G18">
+        <v>50</v>
+      </c>
+      <c r="H18">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A20">
+        <v>13</v>
+      </c>
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20">
+        <v>70</v>
+      </c>
+      <c r="D20">
+        <v>70</v>
+      </c>
+      <c r="E20">
+        <v>80</v>
+      </c>
+      <c r="F20">
+        <v>80</v>
+      </c>
+      <c r="G20">
+        <v>80</v>
+      </c>
+      <c r="H20">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A21">
         <v>14</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B21" t="s">
         <v>11</v>
       </c>
-      <c r="C18">
+      <c r="C21">
         <v>70</v>
       </c>
-      <c r="D18">
+      <c r="D21">
         <v>85</v>
       </c>
-      <c r="E18">
-        <v>50</v>
-      </c>
-      <c r="F18">
+      <c r="E21">
+        <v>50</v>
+      </c>
+      <c r="F21">
         <v>75</v>
       </c>
-      <c r="G18">
+      <c r="G21">
         <v>90</v>
       </c>
-      <c r="H18">
+      <c r="H21">
         <v>95</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A19">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A22">
         <v>15</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B22" t="s">
         <v>20</v>
       </c>
-      <c r="C19">
+      <c r="C22">
         <v>90</v>
       </c>
-      <c r="D19">
-        <v>80</v>
-      </c>
-      <c r="E19">
+      <c r="D22">
+        <v>80</v>
+      </c>
+      <c r="E22">
         <v>70</v>
       </c>
-      <c r="F19">
-        <v>80</v>
-      </c>
-      <c r="G19">
+      <c r="F22">
+        <v>80</v>
+      </c>
+      <c r="G22">
         <v>90</v>
       </c>
-      <c r="H19">
+      <c r="H22">
         <v>95</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B23" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2">
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/Datasets_list.xlsx
+++ b/Datasets_list.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MFI\Documents\GitHub\ML_Dashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim\Documents\OU\Master\afstuderen\Git\ML_Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C02A1D7-7C77-4A48-8206-2DB01F306A45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDD80EAF-1449-467A-B139-B47111A4BC04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{587159C4-2FA1-4D2B-B11E-F39C1D96C62B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{587159C4-2FA1-4D2B-B11E-F39C1D96C62B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>Name</t>
   </si>
@@ -113,20 +113,23 @@
     <t>Logistics</t>
   </si>
   <si>
-    <t>XXXX</t>
-  </si>
-  <si>
     <t>XXXXX</t>
   </si>
   <si>
     <t>xXXXXXX</t>
+  </si>
+  <si>
+    <t>Tennis</t>
+  </si>
+  <si>
+    <t>Nursery</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -145,6 +148,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -170,13 +179,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -192,7 +202,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Kantoorthema">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -508,18 +518,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5F5E0D8-AFDE-4C18-BDE5-CE4646C92338}">
-  <dimension ref="A3:H23"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A3:H24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="30.265625" customWidth="1"/>
-    <col min="3" max="3" width="13.6640625" customWidth="1"/>
-    <col min="4" max="4" width="15.06640625" customWidth="1"/>
-    <col min="6" max="6" width="17.19921875" customWidth="1"/>
-    <col min="7" max="7" width="13.46484375" customWidth="1"/>
-    <col min="8" max="8" width="16.59765625" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="6" max="6" width="17.140625" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" customWidth="1"/>
+    <col min="8" max="8" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
@@ -545,7 +555,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -571,7 +581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
@@ -597,401 +607,416 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2" t="s">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>30</v>
+      </c>
+      <c r="E6">
+        <v>10</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>10</v>
+      </c>
+      <c r="H6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="2">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
-      <c r="G6" s="2">
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
         <v>30</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H7" s="3">
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A7">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
         <v>16</v>
       </c>
-      <c r="C7">
-        <v>10</v>
-      </c>
-      <c r="D7">
+      <c r="C8">
+        <v>10</v>
+      </c>
+      <c r="D8">
         <v>20</v>
       </c>
-      <c r="E7">
-        <v>10</v>
-      </c>
-      <c r="F7">
+      <c r="E8">
+        <v>10</v>
+      </c>
+      <c r="F8">
         <v>20</v>
       </c>
-      <c r="G7">
+      <c r="G8">
         <v>40</v>
       </c>
-      <c r="H7">
+      <c r="H8">
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B8" s="2" t="s">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="3">
+        <v>50</v>
+      </c>
+      <c r="D9" s="3">
+        <v>50</v>
+      </c>
+      <c r="E9" s="3">
         <v>25</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2">
+      <c r="F9" s="3">
+        <v>25</v>
+      </c>
+      <c r="G9" s="3">
+        <v>40</v>
+      </c>
+      <c r="H9" s="3">
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A9">
-        <v>4</v>
-      </c>
-      <c r="B9" t="s">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
         <v>9</v>
       </c>
-      <c r="C9">
-        <v>50</v>
-      </c>
-      <c r="D9">
+      <c r="C10">
+        <v>50</v>
+      </c>
+      <c r="D10">
         <v>70</v>
       </c>
-      <c r="E9">
+      <c r="E10">
         <v>70</v>
       </c>
-      <c r="F9">
-        <v>50</v>
-      </c>
-      <c r="G9">
+      <c r="F10">
+        <v>50</v>
+      </c>
+      <c r="G10">
         <v>55</v>
       </c>
-      <c r="H9">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A10">
-        <v>5</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="H10">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
         <v>12</v>
       </c>
-      <c r="C10">
+      <c r="C11">
         <v>25</v>
       </c>
-      <c r="D10">
+      <c r="D11">
         <v>90</v>
       </c>
-      <c r="E10">
+      <c r="E11">
         <v>20</v>
       </c>
-      <c r="F10">
+      <c r="F11">
         <v>40</v>
       </c>
-      <c r="G10">
-        <v>50</v>
-      </c>
-      <c r="H10">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A11">
-        <v>6</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="G11">
+        <v>50</v>
+      </c>
+      <c r="H11">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
         <v>22</v>
       </c>
-      <c r="C11">
-        <v>10</v>
-      </c>
-      <c r="D11">
-        <v>10</v>
-      </c>
-      <c r="E11">
-        <v>50</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>50</v>
-      </c>
-      <c r="H11">
+      <c r="C12">
+        <v>10</v>
+      </c>
+      <c r="D12">
+        <v>10</v>
+      </c>
+      <c r="E12">
+        <v>50</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>50</v>
+      </c>
+      <c r="H12">
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A12">
-        <v>7</v>
-      </c>
-      <c r="B12" t="s">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
         <v>15</v>
       </c>
-      <c r="C12">
+      <c r="C13">
         <v>20</v>
       </c>
-      <c r="D12">
+      <c r="D13">
         <v>20</v>
-      </c>
-      <c r="E12">
-        <v>20</v>
-      </c>
-      <c r="F12">
-        <v>50</v>
-      </c>
-      <c r="G12">
-        <v>50</v>
-      </c>
-      <c r="H12">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A13">
-        <v>8</v>
-      </c>
-      <c r="B13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13">
-        <v>10</v>
-      </c>
-      <c r="D13">
-        <v>10</v>
       </c>
       <c r="E13">
         <v>20</v>
       </c>
       <c r="F13">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="G13">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="H13">
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14">
+        <v>10</v>
+      </c>
+      <c r="D14">
+        <v>10</v>
+      </c>
+      <c r="E14">
+        <v>20</v>
+      </c>
+      <c r="F14">
+        <v>75</v>
+      </c>
+      <c r="G14">
+        <v>70</v>
+      </c>
+      <c r="H14">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2">
         <v>62.5</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A15">
-        <v>9</v>
-      </c>
-      <c r="B15" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>12</v>
+      </c>
+      <c r="B16" t="s">
         <v>7</v>
       </c>
-      <c r="C15">
-        <v>50</v>
-      </c>
-      <c r="D15">
-        <v>80</v>
-      </c>
-      <c r="E15">
-        <v>50</v>
-      </c>
-      <c r="F15">
-        <v>80</v>
-      </c>
-      <c r="G15">
+      <c r="C16">
+        <v>50</v>
+      </c>
+      <c r="D16">
+        <v>80</v>
+      </c>
+      <c r="E16">
+        <v>50</v>
+      </c>
+      <c r="F16">
+        <v>80</v>
+      </c>
+      <c r="G16">
         <v>70</v>
       </c>
-      <c r="H15">
+      <c r="H16">
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A16">
-        <v>10</v>
-      </c>
-      <c r="B16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>13</v>
+      </c>
+      <c r="B17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17">
         <v>25</v>
       </c>
-      <c r="D16">
-        <v>80</v>
-      </c>
-      <c r="E16">
-        <v>50</v>
-      </c>
-      <c r="F16">
-        <v>50</v>
-      </c>
-      <c r="G16">
+      <c r="D17">
+        <v>80</v>
+      </c>
+      <c r="E17">
+        <v>50</v>
+      </c>
+      <c r="F17">
+        <v>50</v>
+      </c>
+      <c r="G17">
         <v>75</v>
-      </c>
-      <c r="H16">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A17">
-        <v>11</v>
-      </c>
-      <c r="B17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>80</v>
-      </c>
-      <c r="E17">
-        <v>65</v>
-      </c>
-      <c r="F17">
-        <v>80</v>
-      </c>
-      <c r="G17">
-        <v>80</v>
       </c>
       <c r="H17">
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>80</v>
+      </c>
+      <c r="E18">
+        <v>65</v>
+      </c>
+      <c r="F18">
+        <v>80</v>
+      </c>
+      <c r="G18">
+        <v>80</v>
+      </c>
+      <c r="H18">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
         <v>18</v>
       </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="D18">
-        <v>10</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>10</v>
-      </c>
-      <c r="G18">
-        <v>50</v>
-      </c>
-      <c r="H18">
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>10</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>10</v>
+      </c>
+      <c r="G19">
+        <v>50</v>
+      </c>
+      <c r="H19">
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A20">
-        <v>13</v>
-      </c>
-      <c r="B20" t="s">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>16</v>
+      </c>
+      <c r="B21" t="s">
         <v>17</v>
-      </c>
-      <c r="C20">
-        <v>70</v>
-      </c>
-      <c r="D20">
-        <v>70</v>
-      </c>
-      <c r="E20">
-        <v>80</v>
-      </c>
-      <c r="F20">
-        <v>80</v>
-      </c>
-      <c r="G20">
-        <v>80</v>
-      </c>
-      <c r="H20">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A21">
-        <v>14</v>
-      </c>
-      <c r="B21" t="s">
-        <v>11</v>
       </c>
       <c r="C21">
         <v>70</v>
       </c>
       <c r="D21">
+        <v>70</v>
+      </c>
+      <c r="E21">
+        <v>80</v>
+      </c>
+      <c r="F21">
+        <v>80</v>
+      </c>
+      <c r="G21">
+        <v>80</v>
+      </c>
+      <c r="H21">
         <v>85</v>
       </c>
-      <c r="E21">
-        <v>50</v>
-      </c>
-      <c r="F21">
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>17</v>
+      </c>
+      <c r="B22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22">
+        <v>70</v>
+      </c>
+      <c r="D22">
+        <v>85</v>
+      </c>
+      <c r="E22">
+        <v>50</v>
+      </c>
+      <c r="F22">
         <v>75</v>
-      </c>
-      <c r="G21">
-        <v>90</v>
-      </c>
-      <c r="H21">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A22">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22">
-        <v>90</v>
-      </c>
-      <c r="D22">
-        <v>80</v>
-      </c>
-      <c r="E22">
-        <v>70</v>
-      </c>
-      <c r="F22">
-        <v>80</v>
       </c>
       <c r="G22">
         <v>90</v>
@@ -1000,16 +1025,55 @@
         <v>95</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B23" s="2" t="s">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>18</v>
+      </c>
+      <c r="B23" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23">
+        <v>90</v>
+      </c>
+      <c r="D23">
+        <v>80</v>
+      </c>
+      <c r="E23">
+        <v>70</v>
+      </c>
+      <c r="F23">
+        <v>80</v>
+      </c>
+      <c r="G23">
+        <v>90</v>
+      </c>
+      <c r="H23">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>19</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2">
+      <c r="C24" s="3">
+        <v>75</v>
+      </c>
+      <c r="D24" s="3">
+        <v>80</v>
+      </c>
+      <c r="E24" s="3">
+        <v>85</v>
+      </c>
+      <c r="F24" s="3">
+        <v>50</v>
+      </c>
+      <c r="G24" s="3">
+        <v>85</v>
+      </c>
+      <c r="H24" s="3">
         <v>97</v>
       </c>
     </row>
